--- a/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
@@ -935,6 +935,9 @@
       <c r="C60" t="str">
         <v>836_胡姬兰紫_undefined_undefined_1bunch</v>
       </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -993,7 +996,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555553551010955121510685561587.56108155553040403020101010555555141310101010105520100</v>
+        <v>055555553551010955121510685561587.561081555530404030201010105555551413101010101055201010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -939,9 +939,286 @@
         <v>10</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>1</v>
+      </c>
+      <c r="C61" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>860_大菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>798_大菊粉_undefined_undefined_5stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>797_大菊黄_undefined_undefined_5stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>772_格桑花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>773_格桑花白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>854_彼岸花黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>637_干花小盼草红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2</v>
+      </c>
+      <c r="C70" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>875_九星叶红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>3</v>
+      </c>
+      <c r="C76" t="str">
+        <v>516_火焰兰_Crocosmia_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="C77" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>742_袋鼠爪绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F78" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F81" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F82" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F83" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>4</v>
+      </c>
+      <c r="C84" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F84" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F85" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F86" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+      <c r="F88" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>854_彼岸花黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F90" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F91" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>800_树莓_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="str">
+        <v>800_树莓_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F93" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -996,7 +1273,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555553551010955121510685561587.561081555530404030201010105555551413101010101055201010</v>
+        <v>055555553551010955121510685561587.561081555530404030201010105555551413101010101055201010106555455161525810151055581015101551010555555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-7-8.xlsx
@@ -1275,6 +1275,9 @@
       <c r="G2" t="str">
         <v>055555553551010955121510685561587.561081555530404030201010105555551413101010101055201010106555455161525810151055581015101551010555555</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
